--- a/e_commerce_forms/034_seed_order--e_commerce_forms.xlsx
+++ b/e_commerce_forms/034_seed_order--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shipping_state_choices</t>
+          <t>shipping_country_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'ny'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'NY'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'canada'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Canada'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'mexico'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Mexico'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>shipping_country_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'usa'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'USA'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'open'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Open'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'closed'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Closed'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'in_progress'}</t>
+          <t>seed_sale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'In Progress'}</t>
+          <t>Seed Sale</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'seed_sale'}</t>
+          <t>seed_purchase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Seed Sale'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>order_type_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'name':_'seed_purchase'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'name': 'Seed Purchase'}</t>
+          <t>Seed Purchase</t>
         </is>
       </c>
     </row>
